--- a/Data Dictionaries (Upload Here)/DOC/DOC_Data_Dictionary.xlsx
+++ b/Data Dictionaries (Upload Here)/DOC/DOC_Data_Dictionary.xlsx
@@ -1,31 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wonderlyc\Documents\GitHub\Data-Dictionaries\Data Dictionaries (Upload Here)\DOC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ctgovexec-my.sharepoint.com/personal/dan_he_ct_gov/Documents/DanHe_Folders/OPM DataLinkCT/OPM Data Dictionary Enhancement/Agency Data Dictionary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970AF65D-1071-4F01-A11E-8A2EF4D38291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_6C739F2A7BE5FA76E82C792D714E1055BF4437B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FC9B607-082A-4854-AD9F-48B5E93B2540}"/>
   <bookViews>
-    <workbookView xWindow="19092" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-828" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DOC Data Dictionary 3-28-24" sheetId="3" r:id="rId1"/>
+    <sheet name="DOC Data Dictionary 5-28-26" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="141">
   <si>
     <t>Agency</t>
   </si>
@@ -265,19 +277,215 @@
   </si>
   <si>
     <t>Connecticut Department of Correction (DOC)</t>
+  </si>
+  <si>
+    <t>AdmitTownofResidence</t>
+  </si>
+  <si>
+    <t>Current bond amount if applicable</t>
+  </si>
+  <si>
+    <t>InitialDOCAdmissionDate</t>
+  </si>
+  <si>
+    <t>Earliest admission date to DOC</t>
+  </si>
+  <si>
+    <t>Movement sequence number</t>
+  </si>
+  <si>
+    <t>MovementCode</t>
+  </si>
+  <si>
+    <t>Varchar(3)</t>
+  </si>
+  <si>
+    <t>Offender jurisdiction code history</t>
+  </si>
+  <si>
+    <t>Entry, exit or interfacility movement date history</t>
+  </si>
+  <si>
+    <t>Type of movement history</t>
+  </si>
+  <si>
+    <t>Offender sending facility history</t>
+  </si>
+  <si>
+    <t>Offender receiving facility history</t>
+  </si>
+  <si>
+    <t>U,X=Unsentenced,C,G,L=Sentenced history</t>
+  </si>
+  <si>
+    <t>Offender movement sequence (default=1) or higher if more than one movement per day</t>
+  </si>
+  <si>
+    <t>MovementLegalStatus</t>
+  </si>
+  <si>
+    <t>MovementSendingFacility</t>
+  </si>
+  <si>
+    <t>MovementReceivingFacility</t>
+  </si>
+  <si>
+    <t>MovementJurisdictionCode</t>
+  </si>
+  <si>
+    <t>Sentence ID Number</t>
+  </si>
+  <si>
+    <t>Offense Max Sent Length (YRs, MNs, DYs)</t>
+  </si>
+  <si>
+    <t>Offense Susp Sent Lgth (YRs, MNs, DYs)</t>
+  </si>
+  <si>
+    <t>Docket Max Sent Lgth (YRs, MNs, DYs)</t>
+  </si>
+  <si>
+    <t>Docket Max Date</t>
+  </si>
+  <si>
+    <t>Snapshot</t>
+  </si>
+  <si>
+    <t>Movement History</t>
+  </si>
+  <si>
+    <t>Sentence History</t>
+  </si>
+  <si>
+    <t>Sentence sequence number</t>
+  </si>
+  <si>
+    <t>Vachar(7)</t>
+  </si>
+  <si>
+    <t>Integer(7)</t>
+  </si>
+  <si>
+    <t>Offense of conviction history</t>
+  </si>
+  <si>
+    <t>Docket Number</t>
+  </si>
+  <si>
+    <t>Docket number</t>
+  </si>
+  <si>
+    <t>Varchar(16)</t>
+  </si>
+  <si>
+    <t>Charge Count</t>
+  </si>
+  <si>
+    <t>Number of offense of within the docket</t>
+  </si>
+  <si>
+    <t>Varchar(7)</t>
+  </si>
+  <si>
+    <t>Offense Maximum Sentence Length YYYMMDDD</t>
+  </si>
+  <si>
+    <t>Offense Suspended Sentence Length YYYMMDDD</t>
+  </si>
+  <si>
+    <t>Docket Sentence Date</t>
+  </si>
+  <si>
+    <t>Docket Maximum Sentence Length YYYMMDDD</t>
+  </si>
+  <si>
+    <t>Docket End Sentence Date</t>
+  </si>
+  <si>
+    <t>Docket Consecutive Indicator</t>
+  </si>
+  <si>
+    <t>Docket Probation Indicator</t>
+  </si>
+  <si>
+    <t>Offense Consecutive Indicator</t>
+  </si>
+  <si>
+    <t>Within the docket, indicates which offense is consecutive to another offense</t>
+  </si>
+  <si>
+    <t>Offense Probation Indicator</t>
+  </si>
+  <si>
+    <t>Docket Sentence Type</t>
+  </si>
+  <si>
+    <t>Offense Sentence Type</t>
+  </si>
+  <si>
+    <t>Offense Probation Indicator 5=Probation, S=Special Parole, M=Both Probation and Special Parole to follow</t>
+  </si>
+  <si>
+    <t>Docket Probation Indicator 5=Probation, S=Special Parole, M=Both Probation and Special Parole to follow</t>
+  </si>
+  <si>
+    <t>For the offense, D=Determinate, U=Underlying, X=Indeterminate</t>
+  </si>
+  <si>
+    <t>For the entire docket, D=Determinate, U=Underlying, X=Indeterminate</t>
+  </si>
+  <si>
+    <t>Consecutive Docket Indicator</t>
+  </si>
+  <si>
+    <t>Indicates Y/N whether that docket is consecutive to another docket</t>
+  </si>
+  <si>
+    <t>Number indicating which docket is consecutive to that docket</t>
+  </si>
+  <si>
+    <t>Docket Susp Sent Lgth (YRs, MNs, DYs)</t>
+  </si>
+  <si>
+    <t>Docket Suspended Sentence Length YYYMMDDD</t>
+  </si>
+  <si>
+    <t>MostRecentSentLength</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ParoleEligibleDate </t>
+  </si>
+  <si>
+    <t>Date offender eligible for parole release (only currently incarcerated)</t>
+  </si>
+  <si>
+    <t>End sentence date (only currently incarcerated)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -300,8 +508,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -615,20 +838,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +874,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -674,7 +897,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>79</v>
       </c>
@@ -697,7 +920,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>79</v>
       </c>
@@ -720,7 +943,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>79</v>
       </c>
@@ -743,7 +966,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -766,7 +989,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -789,7 +1012,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -812,7 +1035,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>79</v>
       </c>
@@ -835,7 +1058,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>79</v>
       </c>
@@ -858,7 +1081,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>79</v>
       </c>
@@ -881,7 +1104,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>79</v>
       </c>
@@ -904,7 +1127,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>79</v>
       </c>
@@ -927,7 +1150,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>79</v>
       </c>
@@ -950,7 +1173,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>79</v>
       </c>
@@ -973,7 +1196,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>79</v>
       </c>
@@ -996,7 +1219,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -1019,7 +1242,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>79</v>
       </c>
@@ -1042,7 +1265,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>79</v>
       </c>
@@ -1065,7 +1288,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>79</v>
       </c>
@@ -1088,7 +1311,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>79</v>
       </c>
@@ -1111,7 +1334,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>79</v>
       </c>
@@ -1134,7 +1357,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -1157,7 +1380,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -1180,7 +1403,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>79</v>
       </c>
@@ -1203,7 +1426,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>79</v>
       </c>
@@ -1226,7 +1449,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>79</v>
       </c>
@@ -1249,7 +1472,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -1269,6 +1492,1198 @@
         <v>40</v>
       </c>
       <c r="G28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="77.33203125" customWidth="1"/>
+    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>140</v>
+      </c>
+      <c r="F21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" t="s">
+        <v>138</v>
+      </c>
+      <c r="E25" t="s">
+        <v>139</v>
+      </c>
+      <c r="F25" t="s">
+        <v>40</v>
+      </c>
+      <c r="G25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" t="s">
+        <v>137</v>
+      </c>
+      <c r="E26" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" t="s">
+        <v>63</v>
+      </c>
+      <c r="G26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F29" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" t="s">
+        <v>86</v>
+      </c>
+      <c r="G30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" t="s">
+        <v>91</v>
+      </c>
+      <c r="F31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" t="s">
+        <v>86</v>
+      </c>
+      <c r="G32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" t="s">
+        <v>93</v>
+      </c>
+      <c r="F34" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" t="s">
+        <v>105</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35" t="s">
+        <v>106</v>
+      </c>
+      <c r="F35" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" t="s">
+        <v>105</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E36" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" t="s">
+        <v>112</v>
+      </c>
+      <c r="G36" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>79</v>
+      </c>
+      <c r="B37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E37" t="s">
+        <v>114</v>
+      </c>
+      <c r="F37" t="s">
+        <v>41</v>
+      </c>
+      <c r="G37" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" t="s">
+        <v>105</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F38" t="s">
+        <v>115</v>
+      </c>
+      <c r="G38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G39" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" t="s">
+        <v>105</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G40" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" t="s">
+        <v>105</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F41" t="s">
+        <v>40</v>
+      </c>
+      <c r="G41" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" t="s">
+        <v>105</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F42" t="s">
+        <v>32</v>
+      </c>
+      <c r="G42" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" t="s">
+        <v>105</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F43" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F44" t="s">
+        <v>32</v>
+      </c>
+      <c r="G44" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" t="s">
+        <v>67</v>
+      </c>
+      <c r="C45" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F45" t="s">
+        <v>32</v>
+      </c>
+      <c r="G45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" t="s">
+        <v>105</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G46" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>79</v>
+      </c>
+      <c r="B47" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" t="s">
+        <v>105</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" t="s">
+        <v>105</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F48" t="s">
+        <v>40</v>
+      </c>
+      <c r="G48" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>79</v>
+      </c>
+      <c r="B49" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" t="s">
+        <v>105</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F49" t="s">
+        <v>32</v>
+      </c>
+      <c r="G49" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>79</v>
+      </c>
+      <c r="B50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" t="s">
+        <v>105</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F50" t="s">
+        <v>41</v>
+      </c>
+      <c r="G50" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>79</v>
+      </c>
+      <c r="B51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51" t="s">
+        <v>105</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G51" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1278,6 +2693,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="48422074-7e3b-440f-89bb-11ca9694c809">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="0fb435e6-22b0-445c-904d-be41999f5336"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009DB30F33FD16B34CAA58F1E18E2776DF" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="43f178769a943b71f0302c4aaded640c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="0fb435e6-22b0-445c-904d-be41999f5336" xmlns:ns3="48422074-7e3b-440f-89bb-11ca9694c809" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac88f4e0c2aef9b053487fd9151d7613" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1535,29 +2972,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DFE17D6-3443-4E89-8BF7-9CFF61D2DDC9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="48422074-7e3b-440f-89bb-11ca9694c809"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="0fb435e6-22b0-445c-904d-be41999f5336"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="48422074-7e3b-440f-89bb-11ca9694c809">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="0fb435e6-22b0-445c-904d-be41999f5336"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{529FB66F-F798-4FA8-A736-604E47CC8578}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FE320C7-85BA-4E7D-BF4D-A3A351B6EC48}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1575,30 +3016,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{529FB66F-F798-4FA8-A736-604E47CC8578}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DFE17D6-3443-4E89-8BF7-9CFF61D2DDC9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="0fb435e6-22b0-445c-904d-be41999f5336"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="48422074-7e3b-440f-89bb-11ca9694c809"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Dictionaries (Upload Here)/DOC/DOC_Data_Dictionary.xlsx
+++ b/Data Dictionaries (Upload Here)/DOC/DOC_Data_Dictionary.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ctgovexec-my.sharepoint.com/personal/dan_he_ct_gov/Documents/DanHe_Folders/OPM DataLinkCT/OPM Data Dictionary Enhancement/Agency Data Dictionary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_6C739F2A7BE5FA76E82C792D714E1055BF4437B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FC9B607-082A-4854-AD9F-48B5E93B2540}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_6C739F2A7BE5FA76E82C792D714E1055BF4437B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68076208-06E0-40FE-95B0-5EA5D823C5CA}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-828" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DOC Data Dictionary 3-28-24" sheetId="3" r:id="rId1"/>
-    <sheet name="DOC Data Dictionary 5-28-26" sheetId="4" r:id="rId2"/>
+    <sheet name="DOC Data Dictionary 5-28-26" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="131">
   <si>
     <t>Agency</t>
   </si>
@@ -96,9 +95,6 @@
     <t>Bail</t>
   </si>
   <si>
-    <t>Age</t>
-  </si>
-  <si>
     <t>ClaimedEducationLevel</t>
   </si>
   <si>
@@ -123,9 +119,6 @@
     <t>LatestDOCAdmissionDate</t>
   </si>
   <si>
-    <t>ParoleEligibleDate</t>
-  </si>
-  <si>
     <t>CountryofCitizenship</t>
   </si>
   <si>
@@ -153,9 +146,6 @@
     <t>Varchar(37)</t>
   </si>
   <si>
-    <t>TownofResidence</t>
-  </si>
-  <si>
     <t>Date (MM/DD/YYYY)</t>
   </si>
   <si>
@@ -180,15 +170,9 @@
     <t>SnapshotDate</t>
   </si>
   <si>
-    <t>Age of offender as of SnapshotDate</t>
-  </si>
-  <si>
     <t>1st-of-the-month snapshot date on which the offender is actively supervised</t>
   </si>
   <si>
-    <t>Snapshot/Trend</t>
-  </si>
-  <si>
     <t>Offender-declared country of citizenship</t>
   </si>
   <si>
@@ -213,21 +197,12 @@
     <t>Offender-declared resident town</t>
   </si>
   <si>
-    <t>Sentence Date</t>
-  </si>
-  <si>
     <t>Most recent admission date to DOC</t>
   </si>
   <si>
     <t>Most recent movement date within DOC</t>
   </si>
   <si>
-    <t>Date offender eligible for parole release</t>
-  </si>
-  <si>
-    <t>MaximumSentLength</t>
-  </si>
-  <si>
     <t>Integer(5)</t>
   </si>
   <si>
@@ -259,12 +234,6 @@
   </si>
   <si>
     <t>Current detainer</t>
-  </si>
-  <si>
-    <t>Current bond amount</t>
-  </si>
-  <si>
-    <t>End sentence date</t>
   </si>
   <si>
     <t>Maximum sentence length in months</t>
@@ -540,6 +509,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -838,669 +811,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" t="s">
-        <v>77</v>
-      </c>
-      <c r="F15" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>79</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" t="s">
-        <v>66</v>
-      </c>
-      <c r="F17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>79</v>
-      </c>
-      <c r="B18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>79</v>
-      </c>
-      <c r="B19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21" t="s">
-        <v>39</v>
-      </c>
-      <c r="G21" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>79</v>
-      </c>
-      <c r="B22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" t="s">
-        <v>40</v>
-      </c>
-      <c r="G22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" t="s">
-        <v>40</v>
-      </c>
-      <c r="G23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>79</v>
-      </c>
-      <c r="B24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" t="s">
-        <v>40</v>
-      </c>
-      <c r="G24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>79</v>
-      </c>
-      <c r="B25" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" t="s">
-        <v>40</v>
-      </c>
-      <c r="G25" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>79</v>
-      </c>
-      <c r="B26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" t="s">
-        <v>76</v>
-      </c>
-      <c r="F26" t="s">
-        <v>63</v>
-      </c>
-      <c r="G26" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" t="s">
-        <v>47</v>
-      </c>
-      <c r="F27" t="s">
-        <v>41</v>
-      </c>
-      <c r="G27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F28" t="s">
-        <v>40</v>
-      </c>
-      <c r="G28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1539,10 +849,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -1551,21 +861,21 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
@@ -1574,21 +884,21 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -1597,44 +907,44 @@
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
@@ -1643,1048 +953,1048 @@
         <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
       </c>
       <c r="E11" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="G13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
         <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G19" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F20" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="G20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F21" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G22" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F23" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F24" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G24" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E25" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F25" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G25" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E26" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F26" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="G26" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E27" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F27" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G27" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F28" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G28" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B29" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" t="s">
-        <v>104</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="F29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G29" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E30" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F30" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G30" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E31" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="F31" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G31" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C32" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E32" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F32" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G32" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E33" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G33" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E34" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F34" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G34" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F35" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G35" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E36" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="F36" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="G36" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E37" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="F37" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G37" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="F38" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="G38" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B39" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G39" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B40" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G40" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F41" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G41" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C42" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G42" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C43" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F43" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G43" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C44" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F44" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G44" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C45" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F45" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G45" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B46" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C46" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G46" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C47" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G47" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B48" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C48" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F48" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G48" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F49" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G49" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F50" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G50" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C51" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F51" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G51" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2693,6 +2003,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -2703,15 +2022,6 @@
     <TaxCatchAll xmlns="0fb435e6-22b0-445c-904d-be41999f5336"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2973,6 +2283,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{529FB66F-F798-4FA8-A736-604E47CC8578}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DFE17D6-3443-4E89-8BF7-9CFF61D2DDC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -2986,14 +2304,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{529FB66F-F798-4FA8-A736-604E47CC8578}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
